--- a/addresses.xlsx
+++ b/addresses.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
   <si>
     <t>LastName1</t>
   </si>
@@ -103,9 +103,6 @@
   </si>
   <si>
     <t>Liam</t>
-  </si>
-  <si>
-    <t>Susan</t>
   </si>
   <si>
     <t>Miller</t>
@@ -230,7 +227,8 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
   </cellXfs>
@@ -810,21 +808,21 @@
       <c r="B5" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" t="s">
         <v>30</v>
-      </c>
-      <c r="E5" t="s">
-        <v>31</v>
       </c>
       <c r="F5" s="1"/>
       <c r="G5" t="s">
+        <v>31</v>
+      </c>
+      <c r="H5" t="s">
         <v>32</v>
-      </c>
-      <c r="H5" t="s">
-        <v>33</v>
       </c>
       <c r="I5">
         <v>97209</v>
@@ -832,48 +830,48 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
       <c r="E6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H6" t="s">
         <v>37</v>
-      </c>
-      <c r="H6" t="s">
-        <v>38</v>
       </c>
       <c r="I6">
         <v>33132</v>
       </c>
       <c r="J6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>41</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="E7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F7" s="1"/>
       <c r="G7" t="s">
+        <v>42</v>
+      </c>
+      <c r="H7" t="s">
         <v>43</v>
-      </c>
-      <c r="H7" t="s">
-        <v>44</v>
       </c>
       <c r="I7">
         <v>80202</v>
@@ -881,22 +879,22 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
       <c r="E8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F8" s="1"/>
       <c r="G8" t="s">
+        <v>47</v>
+      </c>
+      <c r="H8" t="s">
         <v>48</v>
-      </c>
-      <c r="H8" t="s">
-        <v>49</v>
       </c>
       <c r="I8">
         <v>98101</v>
@@ -904,22 +902,22 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>50</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>51</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
       <c r="E9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F9" s="1"/>
       <c r="G9" t="s">
+        <v>52</v>
+      </c>
+      <c r="H9" t="s">
         <v>53</v>
-      </c>
-      <c r="H9" t="s">
-        <v>54</v>
       </c>
       <c r="I9">
         <v>2110</v>
@@ -927,22 +925,22 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
+        <v>54</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>56</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
       <c r="E10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F10" s="1"/>
       <c r="G10" t="s">
+        <v>57</v>
+      </c>
+      <c r="H10" t="s">
         <v>58</v>
-      </c>
-      <c r="H10" t="s">
-        <v>59</v>
       </c>
       <c r="I10">
         <v>94086</v>
